--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T22:48:13+00:00</t>
+    <t>2024-11-01T00:02:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-01T00:02:03+00:00</t>
+    <t>2024-11-01T10:26:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-01T10:26:43+00:00</t>
+    <t>2024-11-02T14:39:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-02T14:39:00+00:00</t>
+    <t>2024-11-03T14:03:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T14:03:21+00:00</t>
+    <t>2024-11-05T04:19:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T04:19:38+00:00</t>
+    <t>2024-11-06T01:59:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
